--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-786068 4MP dome camera</v>
+        <v>CAM-327389 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 786068</v>
+        <v>Alpha 327389</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 786068</v>
+        <v>Beta 327389</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 786068</v>
+        <v>Gamma 327389</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 786068</v>
+        <v>Alpha 327389</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 786068</v>
+        <v>Beta 327389</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 786068</v>
+        <v>Gamma 327389</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-327389 4MP dome camera</v>
+        <v>CAM-825413 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 327389</v>
+        <v>Alpha 825413</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 327389</v>
+        <v>Beta 825413</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 327389</v>
+        <v>Gamma 825413</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 327389</v>
+        <v>Alpha 825413</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 327389</v>
+        <v>Beta 825413</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 327389</v>
+        <v>Gamma 825413</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-825413 4MP dome camera</v>
+        <v>CAM-149679 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 825413</v>
+        <v>Alpha 149679</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 825413</v>
+        <v>Beta 149679</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 825413</v>
+        <v>Gamma 149679</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 825413</v>
+        <v>Alpha 149679</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 825413</v>
+        <v>Beta 149679</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 825413</v>
+        <v>Gamma 149679</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-149679 4MP dome camera</v>
+        <v>CAM-409701 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 149679</v>
+        <v>Alpha 409701</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 149679</v>
+        <v>Beta 409701</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 149679</v>
+        <v>Gamma 409701</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 149679</v>
+        <v>Alpha 409701</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 149679</v>
+        <v>Beta 409701</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 149679</v>
+        <v>Gamma 409701</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-409701 4MP dome camera</v>
+        <v>CAM-055502 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 409701</v>
+        <v>Alpha 055502</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 409701</v>
+        <v>Beta 055502</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 409701</v>
+        <v>Gamma 055502</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 409701</v>
+        <v>Alpha 055502</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 409701</v>
+        <v>Beta 055502</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 409701</v>
+        <v>Gamma 055502</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-055502 4MP dome camera</v>
+        <v>CAM-971564 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 055502</v>
+        <v>Alpha 971564</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 055502</v>
+        <v>Beta 971564</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 055502</v>
+        <v>Gamma 971564</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 055502</v>
+        <v>Alpha 971564</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 055502</v>
+        <v>Beta 971564</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 055502</v>
+        <v>Gamma 971564</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-971564 4MP dome camera</v>
+        <v>CAM-705943 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 971564</v>
+        <v>Alpha 705943</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 971564</v>
+        <v>Beta 705943</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 971564</v>
+        <v>Gamma 705943</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 971564</v>
+        <v>Alpha 705943</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 971564</v>
+        <v>Beta 705943</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 971564</v>
+        <v>Gamma 705943</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-705943 4MP dome camera</v>
+        <v>CAM-185405 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 705943</v>
+        <v>Alpha 185405</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 705943</v>
+        <v>Beta 185405</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 705943</v>
+        <v>Gamma 185405</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 705943</v>
+        <v>Alpha 185405</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 705943</v>
+        <v>Beta 185405</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 705943</v>
+        <v>Gamma 185405</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-185405 4MP dome camera</v>
+        <v>CAM-123675 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 185405</v>
+        <v>Alpha 123675</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 185405</v>
+        <v>Beta 123675</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 185405</v>
+        <v>Gamma 123675</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 185405</v>
+        <v>Alpha 123675</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 185405</v>
+        <v>Beta 123675</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 185405</v>
+        <v>Gamma 123675</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-123675 4MP dome camera</v>
+        <v>CAM-472685 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 123675</v>
+        <v>Alpha 472685</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 123675</v>
+        <v>Beta 472685</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 123675</v>
+        <v>Gamma 472685</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 123675</v>
+        <v>Alpha 472685</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 123675</v>
+        <v>Beta 472685</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 123675</v>
+        <v>Gamma 472685</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>

--- a/output/xlsx/sup-06-commercial-comparison.xlsx
+++ b/output/xlsx/sup-06-commercial-comparison.xlsx
@@ -421,7 +421,7 @@
         <v>Requirement</v>
       </c>
       <c r="B2" t="str">
-        <v>CAM-472685 4MP dome camera</v>
+        <v>CAM-998359 4MP dome camera</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 472685</v>
+        <v>Alpha 998359</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 472685</v>
+        <v>Beta 998359</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -634,7 +634,7 @@
         <v>UNKNOWN — quoted_quantity_differs (quotationLine.quantity)</v>
       </c>
       <c r="K3" t="str">
-        <v>stored</v>
+        <v>registered</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 472685</v>
+        <v>Gamma 998359</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Alpha 472685</v>
+        <v>Alpha 998359</v>
       </c>
       <c r="B2" t="str">
         <v>AED</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beta 472685</v>
+        <v>Beta 998359</v>
       </c>
       <c r="B3" t="str">
         <v>EUR</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gamma 472685</v>
+        <v>Gamma 998359</v>
       </c>
       <c r="B4" t="str">
         <v>GBP</v>
